--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484336_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484336_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7033</v>
+        <v>3.0194</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5382</v>
+        <v>2.7206</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8349</v>
+        <v>0.2988</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1707</v>
+        <v>0.0163</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.46</v>
+        <v>0.4213</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6307</v>
+        <v>-0.4051</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1996</v>
+        <v>1.1802</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1637</v>
+        <v>1.045</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0359</v>
+        <v>0.1352</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0289</v>
+        <v>-1.1639</v>
       </c>
       <c r="N2" t="n">
         <v>-0.6237</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4052</v>
+        <v>-0.5403</v>
       </c>
       <c r="P2" t="n">
-        <v>0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R2" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S2" t="n">
-        <v>1.287</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3385</v>
+        <v>0.17</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9485</v>
+        <v>0.8033</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3405</v>
+        <v>3.2019</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.3238</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3405</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6565</v>
+        <v>2.8865</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8272</v>
+        <v>2.9483</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1707</v>
+        <v>-0.0618</v>
       </c>
       <c r="G3" t="n">
         <v>0.4318</v>
@@ -688,13 +688,13 @@
         <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7605</v>
+        <v>0.9905</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2175</v>
+        <v>0.3385</v>
       </c>
       <c r="U3" t="n">
-        <v>0.543</v>
+        <v>0.652</v>
       </c>
       <c r="V3" t="n">
         <v>0.4875</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5562</v>
+        <v>2.3709</v>
       </c>
       <c r="E4" t="n">
-        <v>2.094</v>
+        <v>3.3964</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4623</v>
+        <v>-1.0255</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0163</v>
+        <v>2.1707</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4213</v>
+        <v>-0.46</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4051</v>
+        <v>2.6307</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1802</v>
+        <v>3.1996</v>
       </c>
       <c r="K4" t="n">
-        <v>1.045</v>
+        <v>0.1637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1352</v>
+        <v>3.0359</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1639</v>
+        <v>-1.0289</v>
       </c>
       <c r="N4" t="n">
         <v>-0.6237</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5403</v>
+        <v>-0.4052</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5101</v>
+        <v>0.9547</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4566</v>
+        <v>0.1968</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9667</v>
+        <v>0.7579</v>
       </c>
       <c r="V4" t="n">
-        <v>3.2019</v>
+        <v>-1.3405</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3238</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1219</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8582</v>
+        <v>0.7732</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5487</v>
+        <v>1.1642</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6906</v>
+        <v>-0.391</v>
       </c>
       <c r="G5" t="n">
         <v>0.3908</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1986</v>
+        <v>1.1136</v>
       </c>
       <c r="T5" t="n">
-        <v>0.831</v>
+        <v>0.4465</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3675</v>
+        <v>0.6671</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7312</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1473</v>
+        <v>-1.1352</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7015</v>
+        <v>-1.5804</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5542</v>
+        <v>0.4453</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1853</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>1.16</v>
+        <v>1.1721</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1569</v>
+        <v>0.278</v>
       </c>
       <c r="U6" t="n">
-        <v>1.003</v>
+        <v>0.8941</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5398</v>
+        <v>-2.0725</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4141</v>
+        <v>-0.1919</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1257</v>
+        <v>-1.8806</v>
       </c>
       <c r="G7" t="n">
         <v>-2.2795</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0183</v>
+        <v>-1.5511</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.271</v>
+        <v>-1.0488</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7474</v>
+        <v>-0.5022</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5507</v>
+        <v>-2.3012</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4225</v>
+        <v>-0.6063</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1282</v>
+        <v>-1.6949</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0413</v>
+        <v>-1.638</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1011</v>
+        <v>0.0481</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.1423</v>
+        <v>-1.6861</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3095</v>
+        <v>1.3587</v>
       </c>
       <c r="K8" t="n">
-        <v>0.944</v>
+        <v>0.6165</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2535</v>
+        <v>0.7422</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7318</v>
+        <v>-2.9967</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8429</v>
+        <v>-0.5684</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8889</v>
+        <v>-2.4283</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5561</v>
+        <v>-1.5813</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5969</v>
+        <v>-0.9883</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.593</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4373</v>
+        <v>0.3321</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5961</v>
+        <v>-2.3195</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3131</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2831</v>
+        <v>-2.2286</v>
       </c>
       <c r="G9" t="n">
         <v>-1.345</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7823</v>
+        <v>-1.5057</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2105</v>
+        <v>-0.9883</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5718</v>
+        <v>-0.5174</v>
       </c>
       <c r="V9" t="n">
         <v>-0.0549</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.714</v>
+        <v>-2.4529</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8285</v>
+        <v>-0.7059</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8856</v>
+        <v>-1.7469</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.638</v>
+        <v>-3.0413</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0481</v>
+        <v>0.1011</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6861</v>
+        <v>-3.1423</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3587</v>
+        <v>-0.3095</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6165</v>
+        <v>0.944</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7422</v>
+        <v>-1.2535</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9967</v>
+        <v>-2.7318</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5684</v>
+        <v>-0.8429</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4283</v>
+        <v>-1.8889</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9941</v>
+        <v>-1.4582</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2105</v>
+        <v>-0.8803</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7837</v>
+        <v>-0.5779</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3321</v>
+        <v>2.4373</v>
       </c>
       <c r="W10" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.3321</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8794</v>
+        <v>-3.2115</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5268</v>
+        <v>-2.0419</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3526</v>
+        <v>-1.1696</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7067</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4266</v>
+        <v>-0.7587</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.392</v>
+        <v>-0.9071</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9654</v>
+        <v>0.1484</v>
       </c>
       <c r="V11" t="n">
         <v>0.2772</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.653099999999999</v>
+        <v>-4.4428</v>
       </c>
       <c r="E12" t="n">
-        <v>3.801599999999998</v>
+        <v>5.012200000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.454900000000002</v>
+        <v>-9.454799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-11.1862</v>
@@ -1369,7 +1369,7 @@
         <v>4.9129</v>
       </c>
       <c r="L12" t="n">
-        <v>5.4025</v>
+        <v>5.402500000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-21.5016</v>
@@ -1390,19 +1390,19 @@
         <v>12.6971</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.8612</v>
+        <v>-1.6508</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.5936</v>
+        <v>-3.383</v>
       </c>
       <c r="U12" t="n">
-        <v>1.732</v>
+        <v>1.7323</v>
       </c>
       <c r="V12" t="n">
         <v>4.4875</v>
       </c>
       <c r="W12" t="n">
-        <v>6.869999999999999</v>
+        <v>6.87</v>
       </c>
       <c r="X12" t="n">
         <v>-2.3825</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3193</v>
+        <v>3.9322</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4291</v>
+        <v>5.3839</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8903</v>
+        <v>-1.4517</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7221</v>
+        <v>3.8503</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2766</v>
+        <v>-0.4395</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5545</v>
+        <v>4.2898</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7852</v>
+        <v>5.4988</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2591</v>
+        <v>-0.1407</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5261</v>
+        <v>5.6395</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0631</v>
+        <v>-1.6485</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9826</v>
+        <v>-0.2988</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0805</v>
+        <v>-1.3498</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4057</v>
+        <v>0.3907</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.2667</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8084</v>
+        <v>0.6574</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3869</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3357</v>
+        <v>3.3092</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3839</v>
+        <v>1.7213</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0482</v>
+        <v>1.588</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8503</v>
+        <v>1.7221</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4395</v>
+        <v>2.2766</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2898</v>
+        <v>-0.5545</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4988</v>
+        <v>3.7852</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1407</v>
+        <v>3.2591</v>
       </c>
       <c r="L14" t="n">
-        <v>5.6395</v>
+        <v>0.5261</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6485</v>
+        <v>-2.0631</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2988</v>
+        <v>-0.9826</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3498</v>
+        <v>-1.0805</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2058</v>
+        <v>1.3956</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2667</v>
+        <v>-0.1105</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0609</v>
+        <v>1.5061</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>0.3869</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8279</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5895</v>
+        <v>1.6825</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4113</v>
+        <v>1.238</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1782</v>
+        <v>0.4445</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3556</v>
+        <v>3.1351</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9788</v>
+        <v>1.1931</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3768</v>
+        <v>1.942</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7896</v>
+        <v>4.7237</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3328</v>
+        <v>1.9711</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4568</v>
+        <v>2.7527</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.434</v>
+        <v>-1.5886</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.354</v>
+        <v>-0.7779</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0799</v>
+        <v>-0.8107</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4293</v>
+        <v>0.3288</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5752</v>
+        <v>-0.5556</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8541</v>
+        <v>0.8844</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8793</v>
+        <v>1.6249</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7524</v>
+        <v>2.9546</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.873</v>
+        <v>-1.3297</v>
       </c>
       <c r="G16" t="n">
         <v>2.4681</v>
@@ -1702,13 +1702,13 @@
         <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3934</v>
+        <v>0.3522</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.5019</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3108</v>
+        <v>0.8541</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6093</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1858</v>
+        <v>0.2642</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4291</v>
+        <v>0.9058</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.615</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1351</v>
+        <v>1.3556</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1931</v>
+        <v>0.9788</v>
       </c>
       <c r="I17" t="n">
-        <v>1.942</v>
+        <v>0.3768</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7237</v>
+        <v>2.7896</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9711</v>
+        <v>1.3328</v>
       </c>
       <c r="L17" t="n">
-        <v>2.7527</v>
+        <v>1.4568</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5886</v>
+        <v>-1.434</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7779</v>
+        <v>-0.354</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8107</v>
+        <v>-1.0799</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5396</v>
+        <v>1.1039</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3645</v>
+        <v>0.0696</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1751</v>
+        <v>1.0343</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2737</v>
+        <v>-0.9404</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3394</v>
+        <v>0.2383</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6131</v>
+        <v>-1.1787</v>
       </c>
       <c r="G18" t="n">
         <v>0.946</v>
@@ -1858,13 +1858,13 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1964</v>
+        <v>0.1369</v>
       </c>
       <c r="T18" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.279</v>
+        <v>0.1554</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8279</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0112</v>
+        <v>-2.8712</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2903</v>
+        <v>-2.987</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2791</v>
+        <v>0.1157</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2908</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3615</v>
+        <v>0.5014</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.652</v>
+        <v>-0.3486</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0134</v>
+        <v>0.85</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8865</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>5.6531</v>
+        <v>7.0014</v>
       </c>
       <c r="E20" t="n">
         <v>9.454899999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8017</v>
+        <v>-2.4535</v>
       </c>
       <c r="G20" t="n">
         <v>11.1864</v>
@@ -1984,7 +1984,7 @@
         <v>2.4201</v>
       </c>
       <c r="I20" t="n">
-        <v>8.766300000000001</v>
+        <v>8.766299999999999</v>
       </c>
       <c r="J20" t="n">
         <v>21.5019</v>
@@ -2014,13 +2014,13 @@
         <v>8.7905</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8613</v>
+        <v>4.2095</v>
       </c>
       <c r="T20" t="n">
         <v>-1.7322</v>
       </c>
       <c r="U20" t="n">
-        <v>4.593500000000001</v>
+        <v>5.941699999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-4.4875</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484336_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484336_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8865</v>
+        <v>2.3709</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9483</v>
+        <v>3.3964</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0618</v>
+        <v>-1.0255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4318</v>
+        <v>2.1707</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4024</v>
+        <v>-0.46</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9706</v>
+        <v>2.6307</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0004</v>
+        <v>3.1996</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0261</v>
+        <v>0.1637</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0257</v>
+        <v>3.0359</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5686</v>
+        <v>-1.0289</v>
       </c>
       <c r="N3" t="n">
         <v>-0.6237</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9449</v>
+        <v>-0.4052</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9905</v>
+        <v>0.9547</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3385</v>
+        <v>0.1968</v>
       </c>
       <c r="U3" t="n">
-        <v>0.652</v>
+        <v>0.7579</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4875</v>
+        <v>-1.3405</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1219</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3709</v>
+        <v>2.1349</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3964</v>
+        <v>2.1349</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0255</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1707</v>
+        <v>2.1349</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.46</v>
+        <v>0.921</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6307</v>
+        <v>1.214</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1996</v>
+        <v>2.1349</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1637</v>
+        <v>0.921</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0359</v>
+        <v>1.214</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0289</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6237</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4052</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9547</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1968</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7579</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7732</v>
+        <v>0.7516</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1642</v>
+        <v>0.8133</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.391</v>
+        <v>-0.0618</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3908</v>
+        <v>-1.7031</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0131</v>
+        <v>0.4815</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4039</v>
+        <v>-2.1846</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6944</v>
+        <v>-0.1345</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8851</v>
+        <v>1.1051</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8093</v>
+        <v>-1.2396</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3036</v>
+        <v>-1.5686</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8982</v>
+        <v>-0.6237</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4054</v>
+        <v>-0.9449</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1136</v>
+        <v>0.9905</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4465</v>
+        <v>0.3385</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6671</v>
+        <v>0.652</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7312</v>
+        <v>0.4875</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7312</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +902,72 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1352</v>
+        <v>0.607</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5804</v>
+        <v>0.607</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4453</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1853</v>
+        <v>0.607</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5669</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6184</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8817</v>
+        <v>0.607</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3313</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.213</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3036</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8982</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4054</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8941</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0725</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1919</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8806</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2795</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0668</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2128</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8569</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2239</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0807</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1364</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8429</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.2935</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5511</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0488</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5022</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3012</v>
+        <v>0.1663</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6063</v>
+        <v>0.5572</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6949</v>
+        <v>-0.391</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.638</v>
+        <v>-0.2162</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0481</v>
+        <v>-0.0131</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6861</v>
+        <v>-0.2031</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3587</v>
+        <v>1.0874</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6165</v>
+        <v>0.8851</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7422</v>
+        <v>0.2023</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9967</v>
+        <v>-1.3036</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5684</v>
+        <v>-0.8982</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4283</v>
+        <v>-0.4054</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5813</v>
+        <v>1.1136</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9883</v>
+        <v>0.4465</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.593</v>
+        <v>0.6671</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3321</v>
+        <v>-0.7312</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3321</v>
+        <v>-0.7312</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3195</v>
+        <v>-1.1352</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-1.5804</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2286</v>
+        <v>0.4453</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.345</v>
+        <v>-2.1853</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1988</v>
+        <v>-0.5669</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1463</v>
+        <v>-1.6184</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6517</v>
+        <v>-0.8817</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3697</v>
+        <v>0.3313</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2821</v>
+        <v>-1.213</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9967</v>
+        <v>-1.3036</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5684</v>
+        <v>-0.8982</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4283</v>
+        <v>-0.4054</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5057</v>
+        <v>1.1721</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9883</v>
+        <v>0.278</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5174</v>
+        <v>0.8941</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0549</v>
+        <v>-0.1219</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4529</v>
+        <v>-2.3012</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7059</v>
+        <v>-0.6063</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7469</v>
+        <v>-1.6949</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0413</v>
+        <v>-1.638</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1011</v>
+        <v>0.0481</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1423</v>
+        <v>-1.6861</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3095</v>
+        <v>1.3587</v>
       </c>
       <c r="K10" t="n">
-        <v>0.944</v>
+        <v>0.6165</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2535</v>
+        <v>0.7422</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7318</v>
+        <v>-2.9967</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8429</v>
+        <v>-0.5684</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8889</v>
+        <v>-2.4283</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4582</v>
+        <v>-1.5813</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8803</v>
+        <v>-0.9883</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5779</v>
+        <v>-0.593</v>
       </c>
       <c r="V10" t="n">
-        <v>2.4373</v>
+        <v>0.3321</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2115</v>
+        <v>-2.3195</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0419</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1696</v>
+        <v>-2.2286</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7067</v>
+        <v>-1.345</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0875</v>
+        <v>-0.1988</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6192</v>
+        <v>-1.1463</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4353</v>
+        <v>1.6517</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2446</v>
+        <v>0.3697</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8093</v>
+        <v>1.2821</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2714</v>
+        <v>-2.9967</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8429</v>
+        <v>-0.5684</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4285</v>
+        <v>-2.4283</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7587</v>
+        <v>-1.5057</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9071</v>
+        <v>-0.9883</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1484</v>
+        <v>-0.5174</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0.2224</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,307 +1400,323 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4428</v>
+        <v>-2.3795</v>
       </c>
       <c r="E12" t="n">
-        <v>5.012200000000002</v>
+        <v>-0.4989</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.454799999999999</v>
+        <v>-1.8806</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.1862</v>
+        <v>-2.5865</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4202</v>
+        <v>-1.3737</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.7662</v>
+        <v>-1.2128</v>
       </c>
       <c r="J12" t="n">
-        <v>10.3154</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9129</v>
+        <v>-0.5308</v>
       </c>
       <c r="L12" t="n">
-        <v>5.402500000000001</v>
+        <v>1.0807</v>
       </c>
       <c r="M12" t="n">
-        <v>-21.5016</v>
+        <v>-3.1364</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.333</v>
+        <v>-0.8429</v>
       </c>
       <c r="O12" t="n">
-        <v>-14.1687</v>
+        <v>-2.2935</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9067</v>
+        <v>1.7581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.7903</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6971</v>
+        <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6508</v>
+        <v>-1.5511</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.383</v>
+        <v>-1.0488</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7323</v>
+        <v>-0.5022</v>
       </c>
       <c r="V12" t="n">
-        <v>4.4875</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>6.87</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3825</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9322</v>
+        <v>-2.4529</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3839</v>
+        <v>-0.7059</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4517</v>
+        <v>-1.7469</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8503</v>
+        <v>-3.0413</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4395</v>
+        <v>0.1011</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2898</v>
+        <v>-3.1423</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4988</v>
+        <v>-0.3095</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1407</v>
+        <v>0.944</v>
       </c>
       <c r="L13" t="n">
-        <v>5.6395</v>
+        <v>-1.2535</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6485</v>
+        <v>-2.7318</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2988</v>
+        <v>-0.8429</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3498</v>
+        <v>-1.8889</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3907</v>
+        <v>-1.4582</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2667</v>
+        <v>-0.8803</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6574</v>
+        <v>-0.5779</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1052</v>
+        <v>2.4373</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3092</v>
+        <v>-3.2115</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7213</v>
+        <v>-2.0419</v>
       </c>
       <c r="F14" t="n">
-        <v>1.588</v>
+        <v>-1.1696</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7221</v>
+        <v>-3.7067</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2766</v>
+        <v>-2.0875</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5545</v>
+        <v>-1.6192</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7852</v>
+        <v>-0.4353</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2591</v>
+        <v>-1.2446</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5261</v>
+        <v>0.8093</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0631</v>
+        <v>-3.2714</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9826</v>
+        <v>-0.8429</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0805</v>
+        <v>-2.4285</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3956</v>
+        <v>-0.7587</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1105</v>
+        <v>-0.9071</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5061</v>
+        <v>0.1484</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6825</v>
+        <v>-4.4427</v>
       </c>
       <c r="E15" t="n">
-        <v>1.238</v>
+        <v>5.012100000000003</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4445</v>
+        <v>-9.454799999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1351</v>
+        <v>-11.1862</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1931</v>
+        <v>-2.419999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.942</v>
+        <v>-8.7662</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7237</v>
+        <v>10.3154</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9711</v>
+        <v>4.912999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7527</v>
+        <v>5.402600000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5886</v>
+        <v>-21.5016</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7779</v>
+        <v>-7.333000000000002</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8107</v>
+        <v>-14.1687</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1721</v>
+        <v>3.9067</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-8.7903</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>12.6971</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3288</v>
+        <v>-1.650799999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5556</v>
+        <v>-3.383</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8844</v>
+        <v>1.7323</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6093</v>
+        <v>4.4875</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>6.87</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
-      </c>
+        <v>-2.3825</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1728,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6249</v>
+        <v>3.9322</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9546</v>
+        <v>5.3839</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3297</v>
+        <v>-1.4517</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4681</v>
+        <v>3.8503</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3623</v>
+        <v>-0.4395</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1058</v>
+        <v>4.2898</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8006</v>
+        <v>5.4988</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8841</v>
+        <v>-0.1407</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9165</v>
+        <v>5.6395</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3326</v>
+        <v>-1.6485</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5219</v>
+        <v>-0.2988</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8107</v>
+        <v>-1.3498</v>
       </c>
       <c r="P16" t="n">
         <v>-0.586</v>
@@ -1702,28 +1773,33 @@
         <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3522</v>
+        <v>0.3907</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5019</v>
+        <v>-0.2667</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8541</v>
+        <v>0.6574</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6093</v>
+        <v>2.1052</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2642</v>
+        <v>3.3092</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9058</v>
+        <v>1.7213</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.588</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3556</v>
+        <v>1.7221</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9788</v>
+        <v>2.2766</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3768</v>
+        <v>-0.5545</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7896</v>
+        <v>3.7852</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3328</v>
+        <v>3.2591</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4568</v>
+        <v>0.5261</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.434</v>
+        <v>-2.0631</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.354</v>
+        <v>-0.9826</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0799</v>
+        <v>-1.0805</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1039</v>
+        <v>1.3956</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0696</v>
+        <v>-0.1105</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0343</v>
+        <v>1.5061</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9404</v>
+        <v>3.0489</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2383</v>
+        <v>3.0489</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1787</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.946</v>
+        <v>3.0489</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5551</v>
+        <v>1.2279</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3908</v>
+        <v>1.821</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5656</v>
+        <v>3.0489</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9043</v>
+        <v>1.2279</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6613</v>
+        <v>1.821</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6196</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3492</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2704</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1369</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0185</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1554</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8712</v>
+        <v>1.6249</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.987</v>
+        <v>2.9546</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1157</v>
+        <v>-1.3297</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2908</v>
+        <v>2.4681</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5063</v>
+        <v>0.3623</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2156</v>
+        <v>2.1058</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6616</v>
+        <v>4.8006</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8778</v>
+        <v>1.8841</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2161</v>
+        <v>2.9165</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6291</v>
+        <v>-2.3326</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.5219</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.8107</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5014</v>
+        <v>0.3522</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3486</v>
+        <v>-0.5019</v>
       </c>
       <c r="U19" t="n">
-        <v>0.85</v>
+        <v>0.8541</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8865</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,68 +2060,401 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9058</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.6415999999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.3556</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9788</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.7896</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.3328</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1.434</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-1.0799</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.1039</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.0343</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.9404</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1.1787</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.5656</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.9043</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.6196</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.2704</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P. MONES RIERA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.3664</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1.8109</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.6748</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.7431</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.9317</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-1.5886</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.7779</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8107</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.5556</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8844</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D. ZHURAVLOV</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.8712</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.987</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.2908</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.5063</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.6616</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.8778</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2161</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.6291</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.6284999999999999</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.5014</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.3486</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484336_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>7.0014</v>
       </c>
-      <c r="E20" t="n">
-        <v>9.454899999999999</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="E24" t="n">
+        <v>9.4549</v>
+      </c>
+      <c r="F24" t="n">
         <v>-2.4535</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G24" t="n">
         <v>11.1864</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H24" t="n">
         <v>2.4201</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I24" t="n">
         <v>8.766299999999999</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J24" t="n">
         <v>21.5019</v>
       </c>
-      <c r="K20" t="n">
-        <v>7.3329</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="K24" t="n">
+        <v>7.332800000000001</v>
+      </c>
+      <c r="L24" t="n">
         <v>14.169</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M24" t="n">
         <v>-10.3155</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N24" t="n">
         <v>-4.9129</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O24" t="n">
         <v>-5.4026</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P24" t="n">
         <v>-3.9067</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q24" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R24" t="n">
         <v>8.7905</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S24" t="n">
         <v>4.2095</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T24" t="n">
         <v>-1.7322</v>
       </c>
-      <c r="U20" t="n">
-        <v>5.941699999999999</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="U24" t="n">
+        <v>5.9417</v>
+      </c>
+      <c r="V24" t="n">
         <v>-4.4875</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W24" t="n">
         <v>2.3824</v>
       </c>
-      <c r="X20" t="n">
-        <v>-6.869899999999999</v>
-      </c>
+      <c r="X24" t="n">
+        <v>-6.8699</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
